--- a/Account/Ravi_Account_files/pay_temp.xlsx
+++ b/Account/Ravi_Account_files/pay_temp.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SRC\DSA\Account\Ravi_Account_files\Certificate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SRC\DSA\Account\Ravi_Account_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC7981E-E497-488B-85C5-90C5504C82E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{3A9C93F8-B077-4FA8-9048-5E441F3064F4}"/>
+    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="13656" xr2:uid="{3A9C93F8-B077-4FA8-9048-5E441F3064F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -428,49 +428,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -479,7 +458,6 @@
     <xf numFmtId="165" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -487,15 +465,103 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -507,73 +573,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -965,8 +964,8 @@
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="8.77734375" style="1"/>
-    <col min="3" max="3" width="21.21875" style="38" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.21875" style="38" customWidth="1"/>
+    <col min="3" max="3" width="21.21875" style="23" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.21875" style="23" customWidth="1"/>
     <col min="5" max="5" width="24.33203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="23.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="8.77734375" style="1"/>
@@ -974,269 +973,268 @@
   <sheetData>
     <row r="2" spans="3:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C3" s="54" t="s">
+      <c r="C3" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="8"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="43"/>
     </row>
     <row r="4" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C4" s="56"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="9"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="44"/>
     </row>
     <row r="5" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C5" s="56"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="9"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="44"/>
     </row>
     <row r="6" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C6" s="56"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="9"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="44"/>
     </row>
     <row r="7" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C7" s="39"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="11"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="5"/>
     </row>
     <row r="8" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C8" s="39"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="13"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8"/>
     </row>
     <row r="9" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="15"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="47"/>
     </row>
     <row r="10" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C10" s="36" t="s">
+      <c r="C10" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="42"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="16"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="9"/>
     </row>
     <row r="11" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C11" s="37" t="s">
+      <c r="C11" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="43" t="s">
+      <c r="D11" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="11">
         <v>10097</v>
       </c>
     </row>
     <row r="12" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C12" s="37" t="s">
+      <c r="C12" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="44" t="s">
+      <c r="D12" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="F12" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="13" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C13" s="37" t="s">
+      <c r="C13" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="45">
+      <c r="D13" s="30">
         <v>46082</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="11">
         <v>31</v>
       </c>
     </row>
     <row r="14" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C14" s="37" t="s">
+      <c r="C14" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="46" t="s">
+      <c r="D14" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C15" s="37" t="s">
+      <c r="C15" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="47" t="s">
+      <c r="D15" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="19"/>
-      <c r="F15" s="20"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="13"/>
     </row>
     <row r="16" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C16" s="37"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="21"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="14"/>
     </row>
     <row r="17" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C17" s="36" t="s">
+      <c r="C17" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="49" t="s">
+      <c r="D17" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F17" s="22" t="s">
+      <c r="F17" s="15" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="18" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C18" s="37" t="s">
+      <c r="C18" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="50">
+      <c r="D18" s="35">
         <v>37500</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="E18" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="23">
+      <c r="F18" s="16">
         <v>3750</v>
       </c>
     </row>
     <row r="19" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C19" s="37" t="s">
+      <c r="C19" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="51">
+      <c r="D19" s="36">
         <v>5000</v>
       </c>
-      <c r="E19" s="19" t="s">
+      <c r="E19" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F19" s="23" t="s">
+      <c r="F19" s="16" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C20" s="37" t="s">
+      <c r="C20" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="51">
+      <c r="D20" s="36">
         <v>5000</v>
       </c>
-      <c r="E20" s="35" t="s">
+      <c r="E20" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="F20" s="23">
+      <c r="F20" s="16">
         <v>208</v>
       </c>
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C21" s="37" t="s">
+      <c r="C21" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="D21" s="51">
+      <c r="D21" s="36">
         <v>2750</v>
       </c>
-      <c r="E21" s="24"/>
-      <c r="F21" s="25"/>
+      <c r="F21" s="17"/>
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C22" s="37" t="s">
+      <c r="C22" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="51">
+      <c r="D22" s="36">
         <v>4438</v>
       </c>
-      <c r="E22" s="19"/>
-      <c r="F22" s="25"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="17"/>
     </row>
     <row r="23" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C23" s="37"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="25"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="17"/>
     </row>
     <row r="24" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C24" s="40" t="s">
+      <c r="C24" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="D24" s="52">
+      <c r="D24" s="37">
         <v>54688</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="26">
+      <c r="F24" s="18">
         <v>3958</v>
       </c>
     </row>
     <row r="25" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C25" s="36" t="s">
+      <c r="C25" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D25" s="53">
+      <c r="D25" s="38">
         <v>50730</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F25" s="27"/>
+      <c r="F25" s="19"/>
     </row>
     <row r="26" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C26" s="28" t="s">
+      <c r="C26" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="29"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="50"/>
     </row>
     <row r="27" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C27" s="30"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="31"/>
+      <c r="C27" s="51"/>
+      <c r="D27" s="52"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="53"/>
     </row>
     <row r="28" spans="3:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C28" s="32" t="s">
+      <c r="C28" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="34"/>
+      <c r="D28" s="55"/>
+      <c r="E28" s="55"/>
+      <c r="F28" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="C28:F28"/>
     <mergeCell ref="C3:E6"/>
     <mergeCell ref="F3:F6"/>
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.3" footer="0.3"/>
